--- a/Dance_Studio_Revenue_Analysis_2025-2026.xlsx
+++ b/Dance_Studio_Revenue_Analysis_2025-2026.xlsx
@@ -8,13 +8,13 @@
     <sheet state="visible" name="Summary" sheetId="3" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="Z_0207EA4A_148E_474E_954F_530A4F483DE4_.wvu.FilterData">Data_Group!$A$1:$E$1501</definedName>
-    <definedName hidden="1" localSheetId="0" name="Z_0207EA4A_148E_474E_954F_530A4F483DE4_.wvu.FilterData">Data_Group!$A$1:$E$1501</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_785AAC6D_642E_4FEF_A513_83D980064F15_.wvu.FilterData">Data_Group!$A$1:$E$1501</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_785AAC6D_642E_4FEF_A513_83D980064F15_.wvu.FilterData">Data_Group!$A$1:$E$1501</definedName>
     <definedName name="SlicerCache_Table_1_Col_1">#N/A</definedName>
   </definedNames>
   <calcPr/>
   <customWorkbookViews>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{0207EA4A-148E-474E-954F-530A4F483DE4}" name="Фильтр 1"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{785AAC6D-642E-4FEF-A513-83D980064F15}" name="Фильтр 1"/>
   </customWorkbookViews>
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId8"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6668" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6669" uniqueCount="278">
   <si>
     <t>Branch</t>
   </si>
@@ -1017,13 +1017,15 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="3" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="166" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1107,22 +1109,22 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Summary!$A$4:$A$9</c:f>
+              <c:f>Summary!$A$4:$A$10</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Summary!$B$4:$B$9</c:f>
+              <c:f>Summary!$B$4:$B$10</c:f>
               <c:numCache/>
             </c:numRef>
           </c:val>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="1910019777"/>
-        <c:axId val="1049376947"/>
+        <c:axId val="2032850603"/>
+        <c:axId val="1810582776"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1910019777"/>
+        <c:axId val="2032850603"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1174,10 +1176,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1049376947"/>
+        <c:crossAx val="1810582776"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1049376947"/>
+        <c:axId val="1810582776"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1252,7 +1254,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1910019777"/>
+        <c:crossAx val="2032850603"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -1333,22 +1335,22 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Summary!$I$4:$I$9</c:f>
+              <c:f>Summary!$I$4:$I$10</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Summary!$J$4:$J$9</c:f>
+              <c:f>Summary!$J$4:$J$10</c:f>
               <c:numCache/>
             </c:numRef>
           </c:val>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="1360408199"/>
-        <c:axId val="594048725"/>
+        <c:axId val="694691279"/>
+        <c:axId val="1073090789"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1360408199"/>
+        <c:axId val="694691279"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1400,10 +1402,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="594048725"/>
+        <c:crossAx val="1073090789"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="594048725"/>
+        <c:axId val="1073090789"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1478,7 +1480,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1360408199"/>
+        <c:crossAx val="694691279"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -1591,6 +1593,14 @@
               </a:solidFill>
             </c:spPr>
           </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="46BDC6"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
           <c:dLbls>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
@@ -1602,12 +1612,12 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Summary!$D$4:$D$8</c:f>
+              <c:f>Summary!$D$4:$D$9</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Summary!$E$4:$E$8</c:f>
+              <c:f>Summary!$E$4:$E$9</c:f>
               <c:numCache/>
             </c:numRef>
           </c:val>
@@ -1664,7 +1674,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>885825</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="5419725" cy="1647825"/>
@@ -1689,7 +1699,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="5419725" cy="1647825"/>
@@ -54777,10 +54787,10 @@
     </row>
   </sheetData>
   <customSheetViews>
-    <customSheetView guid="{0207EA4A-148E-474E-954F-530A4F483DE4}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{785AAC6D-642E-4FEF-A513-83D980064F15}" filter="1" showAutoFilter="1">
       <autoFilter ref="$A$1:$E$1501"/>
     </customSheetView>
-    <customSheetView guid="{0207EA4A-148E-474E-954F-530A4F483DE4}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{785AAC6D-642E-4FEF-A513-83D980064F15}" filter="1" showAutoFilter="1">
       <autoFilter ref="$A$1:$E$1501"/>
     </customSheetView>
   </customSheetViews>
@@ -63169,8 +63179,8 @@
         <v>272</v>
       </c>
       <c r="B2" s="13">
-        <f>SUM(B10,E9)</f>
-        <v>2301260</v>
+        <f>SUM(B11,E10)</f>
+        <v>2314560</v>
       </c>
       <c r="F2" s="14"/>
       <c r="G2" s="14"/>
@@ -63290,33 +63300,43 @@
       <c r="H8" s="14"/>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="20"/>
+      <c r="B9" s="19"/>
+      <c r="D9" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="E9" s="23">
+        <f>SUMIF(Data_Indiv!F:F, D9, Data_Indiv!D:D)</f>
+        <v>13300</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="19">
-        <f>SUMIF(Data_Group!C:C,A9,Data_Group!D:D)</f>
+      <c r="B10" s="19">
+        <f>SUMIF(Data_Group!C:C,A10,Data_Group!D:D)</f>
         <v>378690</v>
       </c>
-      <c r="D9" s="23" t="s">
+      <c r="D10" s="24" t="s">
         <v>276</v>
       </c>
-      <c r="E9" s="24">
-        <f>SUM(E4:E8)</f>
-        <v>63700</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="23" t="s">
+      <c r="E10" s="25">
+        <f>SUM(E4:E9)</f>
+        <v>77000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="24" t="s">
         <v>276</v>
       </c>
-      <c r="B10" s="24">
-        <f>SUM(B4:B9)</f>
+      <c r="B11" s="25">
+        <f>SUM(B4:B10)</f>
         <v>2237560</v>
       </c>
     </row>
-    <row r="11"/>
-    <row r="26">
-      <c r="B26" s="26"/>
+    <row r="27">
+      <c r="B27" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">
